--- a/data/trans_dic/P39A5_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>82,82; 89,81</t>
+          <t>83,12; 89,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,78; 87,61</t>
+          <t>82,65; 87,65</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84,08; 87,88</t>
+          <t>83,95; 87,79</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,7; 95,56</t>
+          <t>86,39; 94,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,34; 89,15</t>
+          <t>85,42; 89,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,76; 92,45</t>
+          <t>86,92; 93,26</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>82,09; 88,48</t>
+          <t>81,8; 88,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,11; 94,11</t>
+          <t>84,02; 94,79</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,44; 91,71</t>
+          <t>84,24; 91,78</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,89; 90,09</t>
+          <t>85,93; 90,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>62,82; 87,53</t>
+          <t>59,96; 87,5</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,6; 88,12</t>
+          <t>71,21; 88,09</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,56; 91,01</t>
+          <t>86,62; 91,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79,85; 87,91</t>
+          <t>78,47; 87,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83,85; 88,45</t>
+          <t>83,65; 88,57</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón</t>
+          <t>Población que sí diría que estar con dificultad para respirar es un síntoma de que a alguien le está dando un ataque al corazón (tasa de respuesta: 91,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>468849; 508445</t>
+          <t>470579; 507364</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>489151; 517695</t>
+          <t>488382; 517883</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>972744; 1016791</t>
+          <t>971261; 1015754</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>965302; 1063935</t>
+          <t>961890; 1057448</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>758023; 791863</t>
+          <t>758678; 792300</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1736600; 1850443</t>
+          <t>1739814; 1866704</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>542924; 585239</t>
+          <t>541041; 584508</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>722075; 807953</t>
+          <t>721338; 813763</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1283495; 1393879</t>
+          <t>1280395; 1395027</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>743953; 780386</t>
+          <t>744335; 781768</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>634163; 883608</t>
+          <t>605308; 883277</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1342864; 1652765</t>
+          <t>1335590; 1652260</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2776002; 2918806</t>
+          <t>2778139; 2920246</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2672728; 2942438</t>
+          <t>2626326; 2941614</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5495729; 5797475</t>
+          <t>5482791; 5805045</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P39A5_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P39A5_2023-Habitat-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,48%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>83,12; 89,62</t>
+          <t>85,04; 90,2</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>82,65; 87,65</t>
+          <t>83,17; 87,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>83,95; 87,79</t>
+          <t>84,83; 88,31</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>87,47%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>89,05%</t>
+          <t>87,09%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>86,39; 94,97</t>
+          <t>85,17; 89,7</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>85,42; 89,2</t>
+          <t>84,53; 88,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86,92; 93,26</t>
+          <t>85,46; 88,8</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87,16%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>81,8; 88,37</t>
+          <t>80,67; 86,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>84,02; 94,79</t>
+          <t>81,61; 86,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>84,24; 91,78</t>
+          <t>81,91; 85,75</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>81,1%</t>
+          <t>87,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84,4%</t>
+          <t>87,45%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>85,93; 90,25</t>
+          <t>85,23; 89,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>59,96; 87,5</t>
+          <t>85,25; 88,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>71,21; 88,09</t>
+          <t>85,99; 88,74</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>86,82%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>85,37%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>86,62; 91,05</t>
+          <t>85,53; 88,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>78,47; 87,89</t>
+          <t>84,99; 87,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>83,65; 88,57</t>
+          <t>85,56; 87,2</t>
         </is>
       </c>
     </row>
@@ -907,17 +907,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>492382</t>
+          <t>533184</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>503602</t>
+          <t>543963</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>995984</t>
+          <t>1077147</t>
         </is>
       </c>
     </row>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>470579; 507364</t>
+          <t>516571; 547927</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>488382; 517883</t>
+          <t>529259; 557960</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>971261; 1015754</t>
+          <t>1055095; 1098439</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>1006296</t>
+          <t>829757</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>776101</t>
+          <t>858005</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1782398</t>
+          <t>1687762</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>961890; 1057448</t>
+          <t>807932; 850912</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>758678; 792300</t>
+          <t>836260; 876398</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1739814; 1866704</t>
+          <t>1656084; 1720824</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>565732</t>
+          <t>626248</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>759107</t>
+          <t>642283</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1324840</t>
+          <t>1268531</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>541041; 584508</t>
+          <t>602307; 648028</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>721338; 813763</t>
+          <t>623243; 659965</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1280395; 1395027</t>
+          <t>1237067; 1295136</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>764369</t>
+          <t>807550</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>818634</t>
+          <t>890258</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1583003</t>
+          <t>1697808</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>744335; 781768</t>
+          <t>783156; 826277</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>605308; 883277</t>
+          <t>871747; 908832</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1335590; 1652260</t>
+          <t>1669430; 1722880</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2828781</t>
+          <t>2796740</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2857444</t>
+          <t>2934509</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5686225</t>
+          <t>5731249</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2778139; 2920246</t>
+          <t>2755388; 2839553</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2626326; 2941614</t>
+          <t>2899864; 2969986</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5482791; 5805045</t>
+          <t>5675764; 5784167</t>
         </is>
       </c>
     </row>
